--- a/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
+++ b/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec7050e6095d21e4/Escritorio/Tesis/devolucion_AE2/build/_salida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DC47D203F350B0D873BE5F29E5FA04E3EB63DA47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_DC472E8B7652FAD873BE5F29E5FA04E3EB63DA47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
+++ b/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec7050e6095d21e4/Escritorio/Tesis/devolucion_AE2/build/_salida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_DC472E8B7652FAD873BE5F29E5FA04E3EB63DA47" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_EF7FC0DB537A4C5052A15F29E5FA04E3EBD19D46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="645">
   <si>
     <t>Libro de trabajo de la AE2 · Proyecto Final de Grado 2026</t>
   </si>
@@ -256,7 +256,7 @@
     <t>Automatiza la liquidación y elimina las sumas manuales de tiempos de estadía.</t>
   </si>
   <si>
-    <t>Condición inicial: tarifa Estándar vigente ($8.000 por 120 min y $2.500 por cada fracción de 30 min o porción, sin tolerancia) y un turno En Curso. Acción: pedir el resumen del turno a los 120, 121, 150 y 151 min. Resultado: sobreturno de $0, $2.500, $2.500 y $5.000; total = tarifa base + sobreturno + consumos (RN-DER-01 y RN-DER-02). Los importes de la tarifa están pendientes de validación por la gerencia: el acta del 23/09 aprueba la regla, no los valores.</t>
+    <t>Condición inicial: tarifa Estándar vigente ($8.000 por 120 min y $2.500 por cada fracción de 30 min o porción, sin tolerancia) y un turno En Curso. Acción: pedir el resumen del turno a los 120, 121, 150 y 151 min. Resultado: sobreturno de $0, $2.500, $2.500 y $5.000; total = tarifa base + sobreturno + consumos (RN-DER-01 y RN-DER-02). La gerencia aprobó los importes de la tarifa en el acta del 06/10/2026; el acta del 23/09 había aprobado la regla.</t>
   </si>
   <si>
     <t>H-05, H-07, H-16 · Acta 23/09</t>
@@ -364,459 +364,465 @@
     <t>Condición inicial: arqueo cerrado. Acción: exportar el comprobante. Resultado: se descarga un PDF con la guardia, el operador, los turnos, los importes por medio de pago, el total declarado, el total del sistema y la diferencia, en menos de 2 s con 50 turnos.</t>
   </si>
   <si>
+    <t>H-23 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>RF-11</t>
+  </si>
+  <si>
+    <t>El sistema permite al administrador modificar la tarifa vigente y los precios de los artículos.</t>
+  </si>
+  <si>
+    <t>Las tarifas cambian con alta frecuencia (H-07) y no pueden estar fijas en el código.</t>
+  </si>
+  <si>
+    <t>Condición inicial: sesión con rol Administrador y un turno finalizado con tarifa_base $8.000. Acción: cambiar la tarifa vigente a $9.000. Resultado: los turnos nuevos copian $9.000 y el turno finalizado conserva $8.000 y sus importes.</t>
+  </si>
+  <si>
+    <t>H-07 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RF-12</t>
+  </si>
+  <si>
+    <t>El sistema marca en la grilla las habitaciones que superan 30 min en En Limpieza.</t>
+  </si>
+  <si>
+    <t>Could</t>
+  </si>
+  <si>
+    <t>La limpieza hoy no se anota (H-15) ni se mide (H-11); la marca hace visible la demora.</t>
+  </si>
+  <si>
+    <t>Condición inicial: habitación en En Limpieza desde hace más de 30 min. Acción: refrescar la grilla. Resultado: la tarjeta muestra la marca «Demora de limpieza» con los minutos transcurridos; con 30 min o menos no se muestra.</t>
+  </si>
+  <si>
+    <t>H-11, H-15 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RF-13</t>
+  </si>
+  <si>
+    <t>El sistema emite avisos sonoros en el navegador.</t>
+  </si>
+  <si>
+    <t>Won't</t>
+  </si>
+  <si>
+    <t>Queda fuera de este proyecto: el puesto de ventanilla no requiere avisos sonoros y la alerta visual de RF-12 cubre la necesidad.</t>
+  </si>
+  <si>
+    <t>Condición inicial: se genera una alerta operativa (RF-12). Acción: cargar la interfaz. Resultado: la alerta se muestra solo en forma visual y el navegador no reproduce ningún sonido.</t>
+  </si>
+  <si>
+    <t>Decisión de alcance (III.4), sin hallazgo · Acta 23/09</t>
+  </si>
+  <si>
+    <t>No se planifica</t>
+  </si>
+  <si>
+    <t>RNF-01</t>
+  </si>
+  <si>
+    <t>La base de datos rechaza toda modificación y todo borrado de un turno cerrado, de sus pagos y de sus consumos.</t>
+  </si>
+  <si>
+    <t>No funcional</t>
+  </si>
+  <si>
+    <t>Fiabilidad</t>
+  </si>
+  <si>
+    <t>Impide que una sentencia de la aplicación altere lo ya cobrado (H-04, H-22).</t>
+  </si>
+  <si>
+    <t>Condición inicial: turno FINALIZADO con un pago y un consumo en PostgreSQL 16. Acción: ejecutar UPDATE y DELETE desde SQL sobre el turno, sobre su pago y sobre su consumo. Resultado: el motor rechaza las seis sentencias con la excepción de RN-RES-01 (db/verify_inmutabilidad.sql, paso del canal). Alcance: sentencias de la aplicación; el dueño de las tablas puede deshabilitar un trigger, y esa brecha se cierra con el rol de aplicación motel_app, que no es dueño de las tablas (v1.2; db/verify_roles.sql, paso del canal).</t>
+  </si>
+  <si>
+    <t>H-04, H-22, H-23 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RNF-02</t>
+  </si>
+  <si>
+    <t>El backend responde la apertura y el cobro de un turno en 800 ms o menos.</t>
+  </si>
+  <si>
+    <t>Rendimiento</t>
+  </si>
+  <si>
+    <t>El cobro debe resolverse en un paso, sin demorar al cliente en la salida (H-08).</t>
+  </si>
+  <si>
+    <t>Condición inicial: API en el entorno de despliegue con 5 peticiones concurrentes de apertura y 5 de cobro. Acción: repetir 20 veces y medir la latencia. Resultado: el percentil 95 es de 800 ms o menos. La gerencia aprobó el umbral en el acta del 06/10/2026.</t>
+  </si>
+  <si>
+    <t>H-02, H-08, H-14 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RNF-03</t>
+  </si>
+  <si>
+    <t>El sistema no almacena nombre, apellido, DNI, teléfono, correo ni domicilio del cliente.</t>
+  </si>
+  <si>
+    <t>Cumplimiento normativo</t>
+  </si>
+  <si>
+    <t>Minimización de datos: el negocio no necesita identificar al cliente y la Ley 25.326 (art. 4) pide datos adecuados, pertinentes y no excesivos.</t>
+  </si>
+  <si>
+    <t>Condición inicial: esquema creado con db/init.sql. Acción: consultar information_schema.columns. Resultado: ninguna columna de ninguna tabla guarda nombre, apellido, DNI, teléfono, correo ni domicilio del cliente; el cliente se identifica solo por la patente (opcional) o por el tipo Peatón. La retención de la patente se trata en RNF-08.</t>
+  </si>
+  <si>
+    <t>H-08, H-20 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RNF-04</t>
+  </si>
+  <si>
+    <t>El sistema identifica a cada operador y atribuye a su sesión los turnos, cobros y arqueos que ejecuta.</t>
+  </si>
+  <si>
+    <t>Seguridad</t>
+  </si>
+  <si>
+    <t>El cierre ciego necesita saber a quién atribuir un faltante (RF-09) y la AE1 exige delimitar responsabilidades (H-06).</t>
+  </si>
+  <si>
+    <t>Condición inicial: dos conserjes con credenciales propias. Acción: un conserje inicia sesión y ejecuta una apertura y un cobro; desde la consola del navegador se ejecuta document.cookie. Resultado: el token JWT no es visible (cookie httpOnly), el turno y el pago registran el identificador de ese operador y una petición sin token responde 401. La gerencia aprobó el requisito en el acta del 06/10/2026; el mecanismo se decide en el prototipo v2.</t>
+  </si>
+  <si>
+    <t>H-06, H-17 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RNF-05</t>
+  </si>
+  <si>
+    <t>La interfaz se usa sin desplazamiento horizontal en 1366 × 768 px y con controles de al menos 44 × 44 px.</t>
+  </si>
+  <si>
+    <t>Usabilidad</t>
+  </si>
+  <si>
+    <t>Debe operar en la terminal de la ventanilla. La gerencia aprobó el requisito en el acta del 06/10/2026, pero la resolución real de ese monitor no se informó: queda pendiente fecharla.</t>
+  </si>
+  <si>
+    <t>Condición inicial: navegador a 1366 × 768 px. Acción: recorrer apertura, consumo y cobro. Resultado: no aparece barra de desplazamiento horizontal y cada control tiene un área de clic de al menos 44 × 44 px, comprobada con las herramientas del navegador.</t>
+  </si>
+  <si>
+    <t>Sin hallazgo: relevar y fechar la resolución del monitor de la ventanilla · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RNF-06</t>
+  </si>
+  <si>
+    <t>El servicio tiene una disponibilidad mensual de 99,5 % o más.</t>
+  </si>
+  <si>
+    <t>El motel opera las 24 h y la región presenta intermitencias (H-09).</t>
+  </si>
+  <si>
+    <t>Condición inicial: sondeo de /health cada 60 s durante 30 días en el entorno de despliegue. Acción: sumar los minutos sin respuesta. Resultado: 216 min o menos en 30 días (99,5 % de 43.200 min).</t>
+  </si>
+  <si>
+    <t>H-09 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RNF-07</t>
+  </si>
+  <si>
+    <t>Los módulos de liquidación y de caja tienen una cobertura de pruebas de 70 % o más.</t>
+  </si>
+  <si>
+    <t>Mantenibilidad</t>
+  </si>
+  <si>
+    <t>Protege las reglas de cálculo frente a regresiones cuando cambian las tarifas.</t>
+  </si>
+  <si>
+    <t>Condición inicial: canal de integración continua ejecutando pytest con medición de cobertura. Acción: medir la cobertura de los módulos de liquidación y de caja. Resultado: 70 % o más de líneas; el canal falla si baja de ese valor.</t>
+  </si>
+  <si>
+    <t>Decisión de calidad del autor, sin hallazgo · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RNF-08</t>
+  </si>
+  <si>
+    <t>La patente de un turno se elimina dentro de las 24 h posteriores a su cierre.</t>
+  </si>
+  <si>
+    <t>La patente identifica de forma indirecta al titular del vehículo; se conserva mientras el vehículo está en el motel y luego se elimina (Ley 25.326, art. 4, inc. 7). La gerencia aprobó las 24 h en el acta del 06/10/2026 y declaró que necesita la patente por razones de seguridad; informó que no hay indicación del asesor legal.</t>
+  </si>
+  <si>
+    <t>Condición inicial: turno FINALIZADO con patente AE987CD, cerrado hace más de 24 h. Acción: ejecutar la depuración y consultar los turnos cerrados y la tabla de estadía activa. Resultado: ninguna patente de un turno cerrado hace más de 24 h permanece almacenada (la consulta devuelve 0 filas) y los importes del turno quedan intactos, sin deshabilitar los triggers de inmutabilidad.</t>
+  </si>
+  <si>
+    <t>H-08, H-16, H-20 · Acta 23/09</t>
+  </si>
+  <si>
+    <t>RNF-09</t>
+  </si>
+  <si>
+    <t>Ante una pérdida de conexión del navegador, los cronómetros de los turnos continúan en el servidor y la interfaz recupera el estado en 5 s o menos al reconectar.</t>
+  </si>
+  <si>
+    <t>Es la decisión de la AE1 para las intermitencias de internet (H-09); reemplaza la idea de persistencia local en caché, que no se sostiene con el servidor en la nube.</t>
+  </si>
+  <si>
+    <t>Condición inicial: tres turnos En Curso. Acción: cortar la conexión del navegador durante 10 min y restablecerla. Resultado: en 5 s o menos la grilla muestra los tres turnos con los minutos calculados por el servidor (diferencia de 1 min o menos respecto de su reloj), sin turnos perdidos ni duplicados. Durante el corte no se pueden abrir ni cobrar turnos; el procedimiento de contingencia manual no se definió en la sesión del 06/10/2026 y queda pendiente.</t>
+  </si>
+  <si>
+    <t>Matriz de trazabilidad · hallazgo de la AE1 → requisito</t>
+  </si>
+  <si>
+    <t>Se verifica en doble vía. Todo requisito llega a un hallazgo; todo hallazgo llega a un requisito o a una justificación expresa de por qué no derivó ninguno. El silencio no es una decisión.</t>
+  </si>
+  <si>
+    <t>Código (H-01, H-02…)</t>
+  </si>
+  <si>
+    <t>Hallazgo de la AE1 (dato y valor)</t>
+  </si>
+  <si>
+    <t>Fuente (apartado del Cap. II o acta)</t>
+  </si>
+  <si>
+    <t>Requisito(s) derivado(s)</t>
+  </si>
+  <si>
+    <t>Si no deriva: justificación</t>
+  </si>
+  <si>
+    <t>Control de la doble vía</t>
+  </si>
+  <si>
+    <t>H-01</t>
+  </si>
+  <si>
+    <t>13 habitaciones, 3 guardias diarias y unos 30 turnos por día hábil (lunes a jueves) y unos 40 en fin de semana (viernes a domingo). La AE1 original informaba 20 a 30 y 40 a 50; rige lo que la gerencia dijo en la entrevista.</t>
+  </si>
+  <si>
+    <t>AE1 · II.3 (v2) y entrevista, pág. 1</t>
+  </si>
+  <si>
+    <t>H-02</t>
+  </si>
+  <si>
+    <t>El arqueo manual de cada recambio de guardia demora 17 min en promedio (cronometrado: 16, 18 y 17 min).</t>
+  </si>
+  <si>
+    <t>AE1 · II.3 y Anexo I</t>
+  </si>
+  <si>
+    <t>RF-08, RNF-02</t>
+  </si>
+  <si>
+    <t>H-03</t>
+  </si>
+  <si>
+    <t>Tasa de Discrepancia de Caja (TDC): 1 de cada 10 recambios (10 %) presenta faltante o sobrante de efectivo.</t>
+  </si>
+  <si>
+    <t>AE1 · II.3, II.4 (Figura 1)</t>
+  </si>
+  <si>
+    <t>RF-08, RF-09</t>
+  </si>
+  <si>
+    <t>H-04</t>
+  </si>
+  <si>
+    <t>Hallazgo 1: el soporte en papel permite anular un turno físicamente y sin rastro; la TDC no se explica solo por errores aritméticos.</t>
+  </si>
+  <si>
+    <t>AE1 · II.6</t>
+  </si>
+  <si>
+    <t>RF-02, RF-07, RNF-01</t>
+  </si>
+  <si>
+    <t>H-05</t>
+  </si>
+  <si>
+    <t>Hallazgo 2: el arqueo consume sus 17 min en reconstruir a mano la línea de tiempo de cada habitación y en contar los productos consumidos.</t>
+  </si>
+  <si>
+    <t>RF-01, RF-03, RF-04, RF-05</t>
+  </si>
+  <si>
+    <t>H-06</t>
+  </si>
+  <si>
+    <t>El conserje no debe ver el total calculado antes de declarar el efectivo físico, para delimitar su responsabilidad ante faltantes.</t>
+  </si>
+  <si>
+    <t>AE1 · II.5 (político y legal)</t>
+  </si>
+  <si>
+    <t>RF-08, RF-09, RNF-04</t>
+  </si>
+  <si>
+    <t>H-07</t>
+  </si>
+  <si>
+    <t>Las tarifas por turno y por sobreturno se ajustan con alta frecuencia por la inflación.</t>
+  </si>
+  <si>
+    <t>AE1 · II.5 (económico)</t>
+  </si>
+  <si>
+    <t>RF-03, RF-11</t>
+  </si>
+  <si>
+    <t>H-08</t>
+  </si>
+  <si>
+    <t>El cliente valora inmediatez y anonimato: sin formularios de filiación y con cobro en un solo paso.</t>
+  </si>
+  <si>
+    <t>AE1 · II.5 (sociocultural)</t>
+  </si>
+  <si>
+    <t>RNF-02, RNF-03, RNF-08</t>
+  </si>
+  <si>
+    <t>H-09</t>
+  </si>
+  <si>
+    <t>Hay intermitencias de energía e internet: el cronómetro debe vivir en el servidor y el navegador recupera el estado al reconectar.</t>
+  </si>
+  <si>
+    <t>AE1 · II.5 (tecnológico)</t>
+  </si>
+  <si>
+    <t>RNF-06, RNF-09</t>
+  </si>
+  <si>
+    <t>H-10</t>
+  </si>
+  <si>
+    <t>Riesgo de resistencia del personal de conserjería a perder el control manual de la recaudación.</t>
+  </si>
+  <si>
+    <t>AE1 · II.5 (FODA, amenaza)</t>
+  </si>
+  <si>
+    <t>Riesgo de adopción: se gestiona con la capacitación (X.5) y con la usabilidad de RNF-05; no genera un requisito propio.</t>
+  </si>
+  <si>
+    <t>H-11</t>
+  </si>
+  <si>
+    <t>El personal de maestranza y limpieza quedó fuera del relevamiento; los tiempos de limpieza son estimaciones indirectas de conserjería.</t>
+  </si>
+  <si>
+    <t>AE1 · II.2 y II.6 (limitaciones)</t>
+  </si>
+  <si>
+    <t>H-12</t>
+  </si>
+  <si>
+    <t>Exclusiones del alcance de la AE1: liquidación de haberes (gestión contable externa) e interfaz de reservas para clientes (anonimato).</t>
+  </si>
+  <si>
+    <t>AE1 · 1.6</t>
+  </si>
+  <si>
+    <t>Exclusiones de alcance (III.4): nómina e interfaz de reservas quedan fuera del proyecto.</t>
+  </si>
+  <si>
+    <t>H-13</t>
+  </si>
+  <si>
+    <t>El personal de conserjería cumple tres guardias fijas de 8 h: 06:00, 14:00 y 22:00.</t>
+  </si>
+  <si>
+    <t>Entrevista · pág. 1</t>
+  </si>
+  <si>
+    <t>H-14</t>
+  </si>
+  <si>
+    <t>Volumen informado por la gerencia: unos 30 turnos por día entre semana y unos 40 los fines de semana.</t>
+  </si>
+  <si>
+    <t>H-15</t>
+  </si>
+  <si>
+    <t>El estado de cada habitación se lleva con papeles anotadores individuales; la limpieza no se anota.</t>
+  </si>
+  <si>
+    <t>RF-01, RF-07, RF-12</t>
+  </si>
+  <si>
+    <t>H-16</t>
+  </si>
+  <si>
+    <t>Cada anotador registra habitación, hora de entrada y de salida, consumos y patente del vehículo (o «peatón»); cada guardia recibe 20 anotadores.</t>
+  </si>
+  <si>
+    <t>RF-02, RF-03, RF-04, RF-05, RNF-08</t>
+  </si>
+  <si>
+    <t>H-17</t>
+  </si>
+  <si>
+    <t>En el recambio, el conserje suma sus anotadores; el total debe coincidir con el efectivo de la gaveta más los pagos digitales, y se devuelven los 20 anotadores.</t>
+  </si>
+  <si>
+    <t>Entrevista · pág. 2</t>
+  </si>
+  <si>
+    <t>RF-06, RF-08, RNF-04</t>
+  </si>
+  <si>
+    <t>H-18</t>
+  </si>
+  <si>
+    <t>Un faltante se descuenta de la caja de la guardia que cierra y se computa como faltante a auditar por los encargados.</t>
+  </si>
+  <si>
+    <t>H-19</t>
+  </si>
+  <si>
+    <t>Los pagos digitales generan un comprobante del POSNET que se suma en el arqueo; hay un QR en las habitaciones.</t>
+  </si>
+  <si>
+    <t>H-20</t>
+  </si>
+  <si>
+    <t>Los papeles con datos de los huéspedes se archivan físicamente en un depósito bajo llave dentro del establecimiento.</t>
+  </si>
+  <si>
+    <t>RNF-03, RNF-08</t>
+  </si>
+  <si>
+    <t>H-21</t>
+  </si>
+  <si>
+    <t>El motel trabaja bajo las ordenanzas municipales, con habilitación para alojamiento por hora y venta de bebidas alcohólicas las 24 h, y atiende solo a mayores de 18 años.</t>
+  </si>
+  <si>
+    <t>Contexto normativo del entorno (III.1): el motel ya cumple las ordenanzas; no exige funcionalidad al sistema.</t>
+  </si>
+  <si>
+    <t>H-22</t>
+  </si>
+  <si>
+    <t>Los anotadores se cambian por montos menores o se entregan en blanco; la gerencia detecta estas maniobras varias veces al mes.</t>
+  </si>
+  <si>
+    <t>RF-08, RNF-01</t>
+  </si>
+  <si>
     <t>H-23</t>
   </si>
   <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>RF-11</t>
-  </si>
-  <si>
-    <t>El sistema permite al administrador modificar la tarifa vigente y los precios de los artículos.</t>
-  </si>
-  <si>
-    <t>Las tarifas cambian con alta frecuencia (H-07) y no pueden estar fijas en el código.</t>
-  </si>
-  <si>
-    <t>Condición inicial: sesión con rol Administrador y un turno finalizado con tarifa_base $8.000. Acción: cambiar la tarifa vigente a $9.000. Resultado: los turnos nuevos copian $9.000 y el turno finalizado conserva $8.000 y sus importes.</t>
-  </si>
-  <si>
-    <t>H-07</t>
-  </si>
-  <si>
-    <t>RF-12</t>
-  </si>
-  <si>
-    <t>El sistema marca en la grilla las habitaciones que superan 30 min en En Limpieza.</t>
-  </si>
-  <si>
-    <t>Could</t>
-  </si>
-  <si>
-    <t>La limpieza hoy no se anota (H-15) ni se mide (H-11); la marca hace visible la demora.</t>
-  </si>
-  <si>
-    <t>Condición inicial: habitación en En Limpieza desde hace más de 30 min. Acción: refrescar la grilla. Resultado: la tarjeta muestra la marca «Demora de limpieza» con los minutos transcurridos; con 30 min o menos no se muestra.</t>
-  </si>
-  <si>
-    <t>H-11, H-15</t>
-  </si>
-  <si>
-    <t>RF-13</t>
-  </si>
-  <si>
-    <t>El sistema emite avisos sonoros en el navegador.</t>
-  </si>
-  <si>
-    <t>Won't</t>
-  </si>
-  <si>
-    <t>Queda fuera de este proyecto: el puesto de ventanilla no requiere avisos sonoros y la alerta visual de RF-12 cubre la necesidad.</t>
-  </si>
-  <si>
-    <t>Condición inicial: se genera una alerta operativa (RF-12). Acción: cargar la interfaz. Resultado: la alerta se muestra solo en forma visual y el navegador no reproduce ningún sonido.</t>
-  </si>
-  <si>
-    <t>Decisión de alcance (III.4), sin hallazgo</t>
-  </si>
-  <si>
-    <t>No se planifica</t>
-  </si>
-  <si>
-    <t>RNF-01</t>
-  </si>
-  <si>
-    <t>La base de datos rechaza toda modificación y todo borrado de un turno cerrado, de sus pagos y de sus consumos.</t>
-  </si>
-  <si>
-    <t>No funcional</t>
-  </si>
-  <si>
-    <t>Fiabilidad</t>
-  </si>
-  <si>
-    <t>Impide que una sentencia de la aplicación altere lo ya cobrado (H-04, H-22).</t>
-  </si>
-  <si>
-    <t>Condición inicial: turno FINALIZADO con un pago y un consumo en PostgreSQL 16. Acción: ejecutar UPDATE y DELETE desde SQL sobre el turno, sobre su pago y sobre su consumo. Resultado: el motor rechaza las seis sentencias con la excepción de RN-RES-01 (db/verify_inmutabilidad.sql, paso del canal). Alcance: sentencias de la aplicación; el dueño de las tablas puede deshabilitar un trigger, y esa brecha se cierra con el rol de aplicación motel_app, que no es dueño de las tablas (v1.2; db/verify_roles.sql, paso del canal).</t>
-  </si>
-  <si>
-    <t>H-04, H-22, H-23 · Acta 23/09</t>
-  </si>
-  <si>
-    <t>RNF-02</t>
-  </si>
-  <si>
-    <t>El backend responde la apertura y el cobro de un turno en 800 ms o menos.</t>
-  </si>
-  <si>
-    <t>Rendimiento</t>
-  </si>
-  <si>
-    <t>El cobro debe resolverse en un paso, sin demorar al cliente en la salida (H-08).</t>
-  </si>
-  <si>
-    <t>Condición inicial: API en el entorno de despliegue con 5 peticiones concurrentes de apertura y 5 de cobro. Acción: repetir 20 veces y medir la latencia. Resultado: el percentil 95 es de 800 ms o menos. El umbral es una decisión de diseño pendiente de validación.</t>
-  </si>
-  <si>
-    <t>H-02, H-08, H-14</t>
-  </si>
-  <si>
-    <t>RNF-03</t>
-  </si>
-  <si>
-    <t>El sistema no almacena nombre, apellido, DNI, teléfono, correo ni domicilio del cliente.</t>
-  </si>
-  <si>
-    <t>Cumplimiento normativo</t>
-  </si>
-  <si>
-    <t>Minimización de datos: el negocio no necesita identificar al cliente y la Ley 25.326 (art. 4) pide datos adecuados, pertinentes y no excesivos.</t>
-  </si>
-  <si>
-    <t>Condición inicial: esquema creado con db/init.sql. Acción: consultar information_schema.columns. Resultado: ninguna columna de ninguna tabla guarda nombre, apellido, DNI, teléfono, correo ni domicilio del cliente; el cliente se identifica solo por la patente (opcional) o por el tipo Peatón. La retención de la patente se trata en RNF-08.</t>
-  </si>
-  <si>
-    <t>H-08, H-20 · Acta 23/09</t>
-  </si>
-  <si>
-    <t>RNF-04</t>
-  </si>
-  <si>
-    <t>El sistema identifica a cada operador y atribuye a su sesión los turnos, cobros y arqueos que ejecuta.</t>
-  </si>
-  <si>
-    <t>Seguridad</t>
-  </si>
-  <si>
-    <t>El cierre ciego necesita saber a quién atribuir un faltante (RF-09) y la AE1 exige delimitar responsabilidades (H-06).</t>
-  </si>
-  <si>
-    <t>Condición inicial: dos conserjes con credenciales propias. Acción: un conserje inicia sesión y ejecuta una apertura y un cobro; desde la consola del navegador se ejecuta document.cookie. Resultado: el token JWT no es visible (cookie httpOnly), el turno y el pago registran el identificador de ese operador y una petición sin token responde 401. El mecanismo está pendiente de validación.</t>
-  </si>
-  <si>
-    <t>H-06, H-17</t>
-  </si>
-  <si>
-    <t>RNF-05</t>
-  </si>
-  <si>
-    <t>La interfaz se usa sin desplazamiento horizontal en 1366 × 768 px y con controles de al menos 44 × 44 px.</t>
-  </si>
-  <si>
-    <t>Usabilidad</t>
-  </si>
-  <si>
-    <t>Debe operar en la terminal de la ventanilla. La resolución de ese monitor no está relevada: queda pendiente fecharla.</t>
-  </si>
-  <si>
-    <t>Condición inicial: navegador a 1366 × 768 px. Acción: recorrer apertura, consumo y cobro. Resultado: no aparece barra de desplazamiento horizontal y cada control tiene un área de clic de al menos 44 × 44 px, comprobada con las herramientas del navegador.</t>
-  </si>
-  <si>
-    <t>Sin hallazgo: relevar y fechar la resolución del monitor de la ventanilla</t>
-  </si>
-  <si>
-    <t>RNF-06</t>
-  </si>
-  <si>
-    <t>El servicio tiene una disponibilidad mensual de 99,5 % o más.</t>
-  </si>
-  <si>
-    <t>El motel opera las 24 h y la región presenta intermitencias (H-09).</t>
-  </si>
-  <si>
-    <t>Condición inicial: sondeo de /health cada 60 s durante 30 días en el entorno de despliegue. Acción: sumar los minutos sin respuesta. Resultado: 216 min o menos en 30 días (99,5 % de 43.200 min).</t>
-  </si>
-  <si>
-    <t>H-09</t>
-  </si>
-  <si>
-    <t>RNF-07</t>
-  </si>
-  <si>
-    <t>Los módulos de liquidación y de caja tienen una cobertura de pruebas de 70 % o más.</t>
-  </si>
-  <si>
-    <t>Mantenibilidad</t>
-  </si>
-  <si>
-    <t>Protege las reglas de cálculo frente a regresiones cuando cambian las tarifas.</t>
-  </si>
-  <si>
-    <t>Condición inicial: canal de integración continua ejecutando pytest con medición de cobertura. Acción: medir la cobertura de los módulos de liquidación y de caja. Resultado: 70 % o más de líneas; el canal falla si baja de ese valor.</t>
-  </si>
-  <si>
-    <t>Decisión de calidad del autor, sin hallazgo</t>
-  </si>
-  <si>
-    <t>RNF-08</t>
-  </si>
-  <si>
-    <t>La patente de un turno se elimina dentro de las 24 h posteriores a su cierre.</t>
-  </si>
-  <si>
-    <t>La patente identifica de forma indirecta al titular del vehículo; se conserva mientras el vehículo está en el motel y luego se elimina (Ley 25.326, art. 4, inc. 7). Las 24 h son una propuesta pendiente de acordar con la gerencia y su asesor legal.</t>
-  </si>
-  <si>
-    <t>Condición inicial: turno FINALIZADO con patente AE987CD, cerrado hace más de 24 h. Acción: ejecutar la depuración y consultar los turnos cerrados y la tabla de estadía activa. Resultado: ninguna patente de un turno cerrado hace más de 24 h permanece almacenada (la consulta devuelve 0 filas) y los importes del turno quedan intactos, sin deshabilitar los triggers de inmutabilidad.</t>
-  </si>
-  <si>
-    <t>H-08, H-16, H-20</t>
-  </si>
-  <si>
-    <t>RNF-09</t>
-  </si>
-  <si>
-    <t>Ante una pérdida de conexión del navegador, los cronómetros de los turnos continúan en el servidor y la interfaz recupera el estado en 5 s o menos al reconectar.</t>
-  </si>
-  <si>
-    <t>Es la decisión de la AE1 para las intermitencias de internet (H-09); reemplaza la idea de persistencia local en caché, que no se sostiene con el servidor en la nube.</t>
-  </si>
-  <si>
-    <t>Condición inicial: tres turnos En Curso. Acción: cortar la conexión del navegador durante 10 min y restablecerla. Resultado: en 5 s o menos la grilla muestra los tres turnos con los minutos calculados por el servidor (diferencia de 1 min o menos respecto de su reloj), sin turnos perdidos ni duplicados. Durante el corte no se pueden abrir ni cobrar turnos; el procedimiento de contingencia manual queda pendiente de acordar con la gerencia.</t>
-  </si>
-  <si>
-    <t>Matriz de trazabilidad · hallazgo de la AE1 → requisito</t>
-  </si>
-  <si>
-    <t>Se verifica en doble vía. Todo requisito llega a un hallazgo; todo hallazgo llega a un requisito o a una justificación expresa de por qué no derivó ninguno. El silencio no es una decisión.</t>
-  </si>
-  <si>
-    <t>Código (H-01, H-02…)</t>
-  </si>
-  <si>
-    <t>Hallazgo de la AE1 (dato y valor)</t>
-  </si>
-  <si>
-    <t>Fuente (apartado del Cap. II o acta)</t>
-  </si>
-  <si>
-    <t>Requisito(s) derivado(s)</t>
-  </si>
-  <si>
-    <t>Si no deriva: justificación</t>
-  </si>
-  <si>
-    <t>Control de la doble vía</t>
-  </si>
-  <si>
-    <t>H-01</t>
-  </si>
-  <si>
-    <t>13 habitaciones, 3 guardias diarias y unos 30 turnos por día hábil (lunes a jueves) y unos 40 en fin de semana (viernes a domingo). La AE1 original informaba 20 a 30 y 40 a 50; rige lo que la gerencia dijo en la entrevista.</t>
-  </si>
-  <si>
-    <t>AE1 · II.3 (v2) y entrevista, pág. 1</t>
-  </si>
-  <si>
-    <t>H-02</t>
-  </si>
-  <si>
-    <t>El arqueo manual de cada recambio de guardia demora 17 min en promedio (cronometrado: 16, 18 y 17 min).</t>
-  </si>
-  <si>
-    <t>AE1 · II.3 y Anexo I</t>
-  </si>
-  <si>
-    <t>RF-08, RNF-02</t>
-  </si>
-  <si>
-    <t>H-03</t>
-  </si>
-  <si>
-    <t>Tasa de Discrepancia de Caja (TDC): 1 de cada 10 recambios (10 %) presenta faltante o sobrante de efectivo.</t>
-  </si>
-  <si>
-    <t>AE1 · II.3, II.4 (Figura 1)</t>
-  </si>
-  <si>
-    <t>RF-08, RF-09</t>
-  </si>
-  <si>
-    <t>H-04</t>
-  </si>
-  <si>
-    <t>Hallazgo 1: el soporte en papel permite anular un turno físicamente y sin rastro; la TDC no se explica solo por errores aritméticos.</t>
-  </si>
-  <si>
-    <t>AE1 · II.6</t>
-  </si>
-  <si>
-    <t>RF-02, RF-07, RNF-01</t>
-  </si>
-  <si>
-    <t>H-05</t>
-  </si>
-  <si>
-    <t>Hallazgo 2: el arqueo consume sus 17 min en reconstruir a mano la línea de tiempo de cada habitación y en contar los productos consumidos.</t>
-  </si>
-  <si>
-    <t>RF-01, RF-03, RF-04, RF-05</t>
-  </si>
-  <si>
-    <t>H-06</t>
-  </si>
-  <si>
-    <t>El conserje no debe ver el total calculado antes de declarar el efectivo físico, para delimitar su responsabilidad ante faltantes.</t>
-  </si>
-  <si>
-    <t>AE1 · II.5 (político y legal)</t>
-  </si>
-  <si>
-    <t>RF-08, RF-09, RNF-04</t>
-  </si>
-  <si>
-    <t>Las tarifas por turno y por sobreturno se ajustan con alta frecuencia por la inflación.</t>
-  </si>
-  <si>
-    <t>AE1 · II.5 (económico)</t>
-  </si>
-  <si>
-    <t>RF-03, RF-11</t>
-  </si>
-  <si>
-    <t>H-08</t>
-  </si>
-  <si>
-    <t>El cliente valora inmediatez y anonimato: sin formularios de filiación y con cobro en un solo paso.</t>
-  </si>
-  <si>
-    <t>AE1 · II.5 (sociocultural)</t>
-  </si>
-  <si>
-    <t>RNF-02, RNF-03, RNF-08</t>
-  </si>
-  <si>
-    <t>Hay intermitencias de energía e internet: el cronómetro debe vivir en el servidor y el navegador recupera el estado al reconectar.</t>
-  </si>
-  <si>
-    <t>AE1 · II.5 (tecnológico)</t>
-  </si>
-  <si>
-    <t>RNF-06, RNF-09</t>
-  </si>
-  <si>
-    <t>H-10</t>
-  </si>
-  <si>
-    <t>Riesgo de resistencia del personal de conserjería a perder el control manual de la recaudación.</t>
-  </si>
-  <si>
-    <t>AE1 · II.5 (FODA, amenaza)</t>
-  </si>
-  <si>
-    <t>Riesgo de adopción: se gestiona con la capacitación (X.5) y con la usabilidad de RNF-05; no genera un requisito propio.</t>
-  </si>
-  <si>
-    <t>H-11</t>
-  </si>
-  <si>
-    <t>El personal de maestranza y limpieza quedó fuera del relevamiento; los tiempos de limpieza son estimaciones indirectas de conserjería.</t>
-  </si>
-  <si>
-    <t>AE1 · II.2 y II.6 (limitaciones)</t>
-  </si>
-  <si>
-    <t>H-12</t>
-  </si>
-  <si>
-    <t>Exclusiones del alcance de la AE1: liquidación de haberes (gestión contable externa) e interfaz de reservas para clientes (anonimato).</t>
-  </si>
-  <si>
-    <t>AE1 · 1.6</t>
-  </si>
-  <si>
-    <t>Exclusiones de alcance (III.4): nómina e interfaz de reservas quedan fuera del proyecto.</t>
-  </si>
-  <si>
-    <t>H-13</t>
-  </si>
-  <si>
-    <t>El personal de conserjería cumple tres guardias fijas de 8 h: 06:00, 14:00 y 22:00.</t>
-  </si>
-  <si>
-    <t>Entrevista · pág. 1</t>
-  </si>
-  <si>
-    <t>H-14</t>
-  </si>
-  <si>
-    <t>Volumen informado por la gerencia: unos 30 turnos por día entre semana y unos 40 los fines de semana.</t>
-  </si>
-  <si>
-    <t>H-15</t>
-  </si>
-  <si>
-    <t>El estado de cada habitación se lleva con papeles anotadores individuales; la limpieza no se anota.</t>
-  </si>
-  <si>
-    <t>RF-01, RF-07, RF-12</t>
-  </si>
-  <si>
-    <t>H-16</t>
-  </si>
-  <si>
-    <t>Cada anotador registra habitación, hora de entrada y de salida, consumos y patente del vehículo (o «peatón»); cada guardia recibe 20 anotadores.</t>
-  </si>
-  <si>
-    <t>RF-02, RF-03, RF-04, RF-05, RNF-08</t>
-  </si>
-  <si>
-    <t>H-17</t>
-  </si>
-  <si>
-    <t>En el recambio, el conserje suma sus anotadores; el total debe coincidir con el efectivo de la gaveta más los pagos digitales, y se devuelven los 20 anotadores.</t>
-  </si>
-  <si>
-    <t>Entrevista · pág. 2</t>
-  </si>
-  <si>
-    <t>RF-06, RF-08, RNF-04</t>
-  </si>
-  <si>
-    <t>H-18</t>
-  </si>
-  <si>
-    <t>Un faltante se descuenta de la caja de la guardia que cierra y se computa como faltante a auditar por los encargados.</t>
-  </si>
-  <si>
-    <t>H-19</t>
-  </si>
-  <si>
-    <t>Los pagos digitales generan un comprobante del POSNET que se suma en el arqueo; hay un QR en las habitaciones.</t>
-  </si>
-  <si>
-    <t>H-20</t>
-  </si>
-  <si>
-    <t>Los papeles con datos de los huéspedes se archivan físicamente en un depósito bajo llave dentro del establecimiento.</t>
-  </si>
-  <si>
-    <t>RNF-03, RNF-08</t>
-  </si>
-  <si>
-    <t>H-21</t>
-  </si>
-  <si>
-    <t>El motel trabaja bajo las ordenanzas municipales, con habilitación para alojamiento por hora y venta de bebidas alcohólicas las 24 h, y atiende solo a mayores de 18 años.</t>
-  </si>
-  <si>
-    <t>Contexto normativo del entorno (III.1): el motel ya cumple las ordenanzas; no exige funcionalidad al sistema.</t>
-  </si>
-  <si>
-    <t>H-22</t>
-  </si>
-  <si>
-    <t>Los anotadores se cambian por montos menores o se entregan en blanco; la gerencia detecta estas maniobras varias veces al mes.</t>
-  </si>
-  <si>
-    <t>RF-08, RNF-01</t>
-  </si>
-  <si>
     <t>Auditar un balance hacia atrás exige horas de revisión manual, turno por turno.</t>
   </si>
   <si>
@@ -1033,9 +1039,6 @@
     <t>RN-RES-04</t>
   </si>
   <si>
-    <t>H-16, H-20 · pendiente (plazo a acordar con la gerencia y su asesor legal)</t>
-  </si>
-  <si>
     <t>RN-DER-01</t>
   </si>
   <si>
@@ -1045,7 +1048,7 @@
     <t>Si la estadía supera los 120 min, se suma $2.500 por cada fracción de 30 min o porción de excedente; no se aplica tolerancia.</t>
   </si>
   <si>
-    <t>H-05, H-07 · Acta 23/09 (RF-03) · importes pendientes de validación</t>
+    <t>H-05, H-07 · Acta 23/09 (RF-03)</t>
   </si>
   <si>
     <t>RN-DER-02</t>
@@ -1075,7 +1078,7 @@
     <t>Un pago se imputa a la guardia vigente en el instante en que se registra. Un turno que empieza a las 21:30 y se cobra a las 23:30 se arquea en la guardia de las 22:00.</t>
   </si>
   <si>
-    <t>H-13, H-17 · pendiente (llevar a la gerencia)</t>
+    <t>H-13, H-17</t>
   </si>
   <si>
     <t>RN-EXI-01</t>
@@ -2755,124 +2758,124 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
@@ -2880,163 +2883,163 @@
         <v>199</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="34" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D17" s="34"/>
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="34" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D18" s="34" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B19" s="34" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D19" s="34" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B20" s="34" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C20" s="34" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="D20" s="34"/>
     </row>
     <row r="21" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="34" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="34" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B23" s="34" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -3490,13 +3493,13 @@
         <v>94</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J14" s="12">
         <v>4</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L14" s="11" t="str">
         <f t="shared" si="0"/>
@@ -3505,10 +3508,10 @@
     </row>
     <row r="15" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="13" t="s">
         <v>97</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>98</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>43</v>
@@ -3518,22 +3521,22 @@
         <v>91</v>
       </c>
       <c r="F15" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="H15" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="13" t="s">
-        <v>101</v>
-      </c>
       <c r="I15" s="13" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J15" s="13">
         <v>4</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L15" s="11" t="str">
         <f t="shared" si="0"/>
@@ -3542,35 +3545,35 @@
     </row>
     <row r="16" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>103</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>43</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="G16" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="H16" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="H16" s="12" t="s">
-        <v>107</v>
-      </c>
       <c r="I16" s="12" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J16" s="12">
         <v>4</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L16" s="11" t="str">
         <f t="shared" si="0"/>
@@ -3579,35 +3582,35 @@
     </row>
     <row r="17" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="13" t="s">
         <v>108</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>109</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>43</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="G17" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="H17" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="13" t="s">
+      <c r="I17" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="13" t="s">
+      <c r="K17" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="L17" s="11" t="str">
         <f t="shared" si="0"/>
@@ -3616,28 +3619,28 @@
     </row>
     <row r="18" spans="1:12" ht="126" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="C18" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="D18" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F18" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="H18" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>48</v>
@@ -3655,31 +3658,31 @@
     </row>
     <row r="19" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="C19" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>123</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>124</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F19" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="H19" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="H19" s="13" t="s">
-        <v>127</v>
-      </c>
       <c r="I19" s="13" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J19" s="13">
         <v>3</v>
@@ -3694,28 +3697,28 @@
     </row>
     <row r="20" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="C20" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>130</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F20" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="H20" s="12" t="s">
         <v>132</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>133</v>
       </c>
       <c r="I20" s="12" t="s">
         <v>48</v>
@@ -3731,33 +3734,33 @@
         <v>Fila completa</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="C21" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>135</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>136</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F21" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="H21" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="H21" s="13" t="s">
-        <v>139</v>
-      </c>
       <c r="I21" s="13" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J21" s="13">
         <v>3</v>
@@ -3770,33 +3773,33 @@
         <v>Fila completa</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="C22" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>142</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>44</v>
       </c>
       <c r="F22" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="H22" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="H22" s="12" t="s">
-        <v>145</v>
-      </c>
       <c r="I22" s="12" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J22" s="12">
         <v>2</v>
@@ -3811,37 +3814,37 @@
     </row>
     <row r="23" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="13" t="s">
-        <v>147</v>
-      </c>
       <c r="C23" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>117</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>118</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>91</v>
       </c>
       <c r="F23" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="H23" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="H23" s="13" t="s">
-        <v>150</v>
-      </c>
       <c r="I23" s="13" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J23" s="13">
         <v>4</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L23" s="11" t="str">
         <f t="shared" si="0"/>
@@ -3850,70 +3853,70 @@
     </row>
     <row r="24" spans="1:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>152</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>153</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>91</v>
       </c>
       <c r="F24" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="G24" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="H24" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="H24" s="12" t="s">
-        <v>156</v>
-      </c>
       <c r="I24" s="12" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J24" s="12">
         <v>3</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L24" s="11" t="str">
         <f t="shared" si="0"/>
         <v>Fila completa</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="114" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="138" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>158</v>
-      </c>
       <c r="C25" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="H25" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="13" t="s">
-        <v>161</v>
-      </c>
       <c r="I25" s="13" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J25" s="13">
         <v>3</v>
@@ -3928,37 +3931,37 @@
     </row>
     <row r="26" spans="1:12" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>163</v>
-      </c>
       <c r="C26" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>91</v>
       </c>
       <c r="F26" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="G26" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G26" s="12" t="s">
-        <v>165</v>
-      </c>
       <c r="H26" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J26" s="12">
         <v>4</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L26" s="11" t="str">
         <f t="shared" si="0"/>
@@ -6988,7 +6991,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -6998,7 +7001,7 @@
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -7008,33 +7011,33 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="C5" s="13" t="s">
         <v>175</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>176</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>41</v>
@@ -7047,16 +7050,16 @@
     </row>
     <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="C6" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>179</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>180</v>
       </c>
       <c r="E6" s="12"/>
       <c r="F6" s="11" t="str">
@@ -7066,16 +7069,16 @@
     </row>
     <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="C7" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="D7" s="13" t="s">
         <v>183</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>184</v>
       </c>
       <c r="E7" s="13"/>
       <c r="F7" s="11" t="str">
@@ -7085,16 +7088,16 @@
     </row>
     <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="C8" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="12" t="s">
         <v>187</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>188</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="11" t="str">
@@ -7104,16 +7107,16 @@
     </row>
     <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="C9" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>190</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>191</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="11" t="str">
@@ -7123,16 +7126,16 @@
     </row>
     <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="C10" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>194</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>195</v>
       </c>
       <c r="E10" s="12"/>
       <c r="F10" s="11" t="str">
@@ -7142,7 +7145,7 @@
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>196</v>
@@ -7180,16 +7183,16 @@
     </row>
     <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="11" t="str">
@@ -7199,17 +7202,17 @@
     </row>
     <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F14" s="11" t="str">
         <f t="shared" si="0"/>
@@ -7218,16 +7221,16 @@
     </row>
     <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="11" t="str">
@@ -7237,17 +7240,17 @@
     </row>
     <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F16" s="11" t="str">
         <f t="shared" si="0"/>
@@ -7256,13 +7259,13 @@
     </row>
     <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>79</v>
@@ -7275,16 +7278,16 @@
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>219</v>
-      </c>
       <c r="D18" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="11" t="str">
@@ -7294,16 +7297,16 @@
     </row>
     <row r="19" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="11" t="str">
@@ -7313,16 +7316,16 @@
     </row>
     <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="11" t="str">
@@ -7332,16 +7335,16 @@
     </row>
     <row r="21" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="11" t="str">
@@ -7351,16 +7354,16 @@
     </row>
     <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="11" t="str">
@@ -7370,13 +7373,13 @@
     </row>
     <row r="23" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>69</v>
@@ -7389,16 +7392,16 @@
     </row>
     <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="11" t="str">
@@ -7408,17 +7411,17 @@
     </row>
     <row r="25" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F25" s="11" t="str">
         <f t="shared" si="0"/>
@@ -7427,16 +7430,16 @@
     </row>
     <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="11" t="str">
@@ -7446,16 +7449,16 @@
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>94</v>
+        <v>246</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="11" t="str">
@@ -7465,17 +7468,17 @@
     </row>
     <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>248</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>246</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F28" s="11" t="str">
         <f t="shared" si="0"/>
@@ -7871,7 +7874,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -7882,7 +7885,7 @@
     </row>
     <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -7893,30 +7896,30 @@
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>49</v>
@@ -7928,18 +7931,18 @@
         <v>49</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>49</v>
@@ -7951,18 +7954,18 @@
         <v>49</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>49</v>
@@ -7974,18 +7977,18 @@
         <v>49</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>49</v>
@@ -7997,18 +8000,18 @@
         <v>49</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>49</v>
@@ -8020,18 +8023,18 @@
         <v>49</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>49</v>
@@ -8043,18 +8046,18 @@
         <v>49</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>49</v>
@@ -8066,18 +8069,18 @@
         <v>49</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>49</v>
@@ -8089,18 +8092,18 @@
         <v>49</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>49</v>
@@ -8112,105 +8115,105 @@
         <v>49</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>49</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>49</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>49</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8500,7 +8503,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -8510,7 +8513,7 @@
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -8520,119 +8523,119 @@
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>305</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>308</v>
-      </c>
       <c r="F6" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>95</v>
+        <v>310</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F9" s="13" t="s">
         <v>55</v>
@@ -8640,39 +8643,39 @@
     </row>
     <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>84</v>
@@ -8680,19 +8683,19 @@
     </row>
     <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>95</v>
+        <v>310</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>79</v>
@@ -8700,67 +8703,67 @@
     </row>
     <row r="13" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -8770,7 +8773,7 @@
     </row>
     <row r="17" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -8780,7 +8783,7 @@
     </row>
     <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
@@ -8790,7 +8793,7 @@
     </row>
     <row r="19" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -8800,7 +8803,7 @@
     </row>
     <row r="20" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -8810,7 +8813,7 @@
     </row>
     <row r="21" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B21" s="13"/>
       <c r="C21" s="13"/>
@@ -8820,7 +8823,7 @@
     </row>
     <row r="22" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -8830,7 +8833,7 @@
     </row>
     <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -8840,7 +8843,7 @@
     </row>
     <row r="24" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -8850,7 +8853,7 @@
     </row>
     <row r="25" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -8860,7 +8863,7 @@
     </row>
     <row r="26" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -8870,7 +8873,7 @@
     </row>
     <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -8880,7 +8883,7 @@
     </row>
     <row r="28" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -8890,7 +8893,7 @@
     </row>
     <row r="29" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -8900,7 +8903,7 @@
     </row>
     <row r="30" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -8910,7 +8913,7 @@
     </row>
     <row r="31" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -8920,7 +8923,7 @@
     </row>
     <row r="32" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -8930,7 +8933,7 @@
     </row>
     <row r="33" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
@@ -8940,7 +8943,7 @@
     </row>
     <row r="34" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -8950,7 +8953,7 @@
     </row>
     <row r="35" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -8960,7 +8963,7 @@
     </row>
     <row r="36" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -8970,7 +8973,7 @@
     </row>
     <row r="37" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -8980,7 +8983,7 @@
     </row>
     <row r="38" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
@@ -8990,7 +8993,7 @@
     </row>
     <row r="39" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B39" s="13"/>
       <c r="C39" s="13"/>
@@ -9000,7 +9003,7 @@
     </row>
     <row r="40" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
@@ -9042,7 +9045,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -9051,7 +9054,7 @@
     </row>
     <row r="2" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -9060,33 +9063,33 @@
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>49</v>
@@ -9094,16 +9097,16 @@
     </row>
     <row r="6" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>49</v>
@@ -9111,84 +9114,84 @@
     </row>
     <row r="7" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>387</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>386</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>387</v>
-      </c>
       <c r="E8" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>49</v>
@@ -9196,16 +9199,16 @@
     </row>
     <row r="12" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>49</v>
@@ -9213,53 +9216,53 @@
     </row>
     <row r="13" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
+        <v>409</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>407</v>
-      </c>
       <c r="E15" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -9504,7 +9507,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -9515,7 +9518,7 @@
     </row>
     <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -9526,25 +9529,25 @@
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
@@ -9552,19 +9555,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G5" s="13">
         <f>SUMIF($C$32:$C$59,A5,$H$32:$H$59)</f>
@@ -9576,19 +9579,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G6" s="12">
         <f>SUMIF($C$32:$C$59,A6,$H$32:$H$59)</f>
@@ -9600,19 +9603,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G7" s="13">
         <f>SUMIF($C$32:$C$59,A7,$H$32:$H$59)</f>
@@ -9624,19 +9627,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G8" s="12">
         <f>SUMIF($C$32:$C$59,A8,$H$32:$H$59)</f>
@@ -9689,12 +9692,12 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B16" s="7">
         <v>1</v>
@@ -9702,7 +9705,7 @@
     </row>
     <row r="17" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B17" s="7">
         <v>12</v>
@@ -9710,7 +9713,7 @@
     </row>
     <row r="18" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B18" s="7">
         <v>16</v>
@@ -9718,7 +9721,7 @@
     </row>
     <row r="19" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B19" s="8">
         <f>IF(COUNT(B16:B18)=3,B16*B17*B18,"")</f>
@@ -9727,18 +9730,18 @@
     </row>
     <row r="20" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B20" s="7">
         <v>16</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B21" s="8">
         <f>IF(B19="","",B19-N(B20))</f>
@@ -9747,7 +9750,7 @@
     </row>
     <row r="22" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B22" s="8">
         <f>SUM(G5:G12)</f>
@@ -9756,7 +9759,7 @@
     </row>
     <row r="23" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B23" s="8">
         <f>IF(B21="","",B21-B22)</f>
@@ -9765,15 +9768,15 @@
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C26" s="40"/>
       <c r="D26" s="40"/>
@@ -9782,10 +9785,10 @@
     </row>
     <row r="27" spans="1:8" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B27" s="39" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C27" s="40"/>
       <c r="D27" s="40"/>
@@ -9794,10 +9797,10 @@
     </row>
     <row r="28" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="40"/>
@@ -9806,47 +9809,47 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>33</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C32" s="13">
         <v>1</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E32" s="13">
         <v>0</v>
@@ -9864,16 +9867,16 @@
     </row>
     <row r="33" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C33" s="12">
         <v>1</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E33" s="12">
         <v>0</v>
@@ -9894,7 +9897,7 @@
         <v>41</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C34" s="13">
         <v>2</v>
@@ -9921,7 +9924,7 @@
         <v>50</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C35" s="12">
         <v>2</v>
@@ -9948,7 +9951,7 @@
         <v>55</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C36" s="13">
         <v>2</v>
@@ -9975,7 +9978,7 @@
         <v>60</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C37" s="12">
         <v>2</v>
@@ -10002,7 +10005,7 @@
         <v>65</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C38" s="13">
         <v>2</v>
@@ -10029,7 +10032,7 @@
         <v>69</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C39" s="12">
         <v>2</v>
@@ -10056,7 +10059,7 @@
         <v>74</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C40" s="13">
         <v>2</v>
@@ -10080,10 +10083,10 @@
     </row>
     <row r="41" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C41" s="12">
         <v>2</v>
@@ -10107,10 +10110,10 @@
     </row>
     <row r="42" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C42" s="13">
         <v>2</v>
@@ -10134,10 +10137,10 @@
     </row>
     <row r="43" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C43" s="12">
         <v>2</v>
@@ -10161,16 +10164,16 @@
     </row>
     <row r="44" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C44" s="13">
         <v>2</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E44" s="13">
         <v>7</v>
@@ -10191,7 +10194,7 @@
         <v>79</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C45" s="12">
         <v>3</v>
@@ -10218,7 +10221,7 @@
         <v>84</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C46" s="13">
         <v>3</v>
@@ -10242,10 +10245,10 @@
     </row>
     <row r="47" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C47" s="12">
         <v>3</v>
@@ -10269,10 +10272,10 @@
     </row>
     <row r="48" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C48" s="13">
         <v>3</v>
@@ -10296,10 +10299,10 @@
     </row>
     <row r="49" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C49" s="12">
         <v>3</v>
@@ -10323,10 +10326,10 @@
     </row>
     <row r="50" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C50" s="13">
         <v>3</v>
@@ -10350,16 +10353,16 @@
     </row>
     <row r="51" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C51" s="12">
         <v>3</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E51" s="12">
         <v>0</v>
@@ -10380,7 +10383,7 @@
         <v>89</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C52" s="13">
         <v>4</v>
@@ -10404,10 +10407,10 @@
     </row>
     <row r="53" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C53" s="12">
         <v>4</v>
@@ -10431,16 +10434,16 @@
     </row>
     <row r="54" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C54" s="13">
         <v>4</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E54" s="13">
         <v>0</v>
@@ -10458,10 +10461,10 @@
     </row>
     <row r="55" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C55" s="12">
         <v>4</v>
@@ -10485,10 +10488,10 @@
     </row>
     <row r="56" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C56" s="13">
         <v>4</v>
@@ -10512,16 +10515,16 @@
     </row>
     <row r="57" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C57" s="12">
         <v>4</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E57" s="12">
         <v>10</v>
@@ -10539,16 +10542,16 @@
     </row>
     <row r="58" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C58" s="13">
         <v>4</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E58" s="13">
         <v>0</v>
@@ -10566,16 +10569,16 @@
     </row>
     <row r="59" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C59" s="12">
         <v>4</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E59" s="12">
         <v>0</v>
@@ -10593,7 +10596,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="28" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E60" s="8">
         <f>SUM(E32:E59)</f>
@@ -10640,7 +10643,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -10651,7 +10654,7 @@
     </row>
     <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
@@ -10662,40 +10665,40 @@
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C5" s="13">
         <f>Iteraciones!E60</f>
         <v>71</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E5" s="29">
         <v>21565</v>
@@ -10705,22 +10708,22 @@
         <v>1531115</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C6" s="12">
         <f>Iteraciones!F60</f>
         <v>42</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E6" s="31">
         <v>21565</v>
@@ -10730,22 +10733,22 @@
         <v>905730</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C7" s="13">
         <f>Iteraciones!G60</f>
         <v>63</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E7" s="29">
         <v>21565</v>
@@ -10755,21 +10758,21 @@
         <v>1358595</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C8" s="12">
         <v>1</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E8" s="31">
         <v>0</v>
@@ -10779,21 +10782,21 @@
         <v>0</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C9" s="13">
         <v>1</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E9" s="29">
         <v>0</v>
@@ -10803,21 +10806,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C10" s="12">
         <v>1</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E10" s="31">
         <v>120000</v>
@@ -10827,21 +10830,21 @@
         <v>120000</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C11" s="13">
         <v>3</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E11" s="29">
         <v>40000</v>
@@ -10851,21 +10854,21 @@
         <v>120000</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C12" s="12">
         <v>12</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E12" s="31">
         <v>30129</v>
@@ -10875,21 +10878,21 @@
         <v>361548</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C13" s="13">
         <v>12</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E13" s="29">
         <v>1540</v>
@@ -10899,21 +10902,21 @@
         <v>18480</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C14" s="12">
         <v>1</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E14" s="31">
         <v>9500</v>
@@ -10923,21 +10926,21 @@
         <v>9500</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C15" s="13">
         <v>12</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E15" s="29">
         <v>20000</v>
@@ -10947,7 +10950,7 @@
         <v>240000</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -11180,7 +11183,7 @@
     </row>
     <row r="36" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E36" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F36" s="20">
         <f>SUM(F5:F34)</f>
@@ -11189,7 +11192,7 @@
     </row>
     <row r="37" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E37" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F37" s="21">
         <f>SUMIF($A$5:$A$34,"Humanos",$C$5:$C$34)</f>
@@ -11198,7 +11201,7 @@
     </row>
     <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E38" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F38" s="21" t="str">
         <f>IF(Iteraciones!$B$21="","Falta el presupuesto efectivo",IF(F37=Iteraciones!$B$21,"Coherente",IF(F37&gt;Iteraciones!$B$21,"Excede el presupuesto","No agota el presupuesto: revisar")))</f>
@@ -11233,265 +11236,265 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
     </row>
     <row r="2" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="36" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B2" s="37"/>
       <c r="C2" s="37"/>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B5" s="23">
         <f>COUNTIF(Catálogo!$A$5:$A$201,"?*")</f>
         <v>22</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B6" s="23">
         <f>COUNTIFS(Catálogo!$A$5:$A$201,"?*",Catálogo!$G$5:$G$201,"?*")</f>
         <v>22</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B7" s="23">
         <f>COUNTIFS(Catálogo!$A$5:$A$201,"?*",Catálogo!$H$5:$H$201,"?*")</f>
         <v>22</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B8" s="23">
         <f>COUNTIFS(Catálogo!$A$5:$A$201,"?*",Catálogo!$C$5:$C$201,"No funcional")</f>
         <v>9</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B9" s="23">
         <f>COUNTIFS(Catálogo!$C$5:$C$201,"No funcional",Catálogo!$D$5:$D$201,"")</f>
         <v>0</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B10" s="23">
         <f>COUNTIFS(Catálogo!$A$5:$A$201,"?*",Catálogo!$E$5:$E$201,"Must")</f>
         <v>15</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B11" s="23">
         <f>COUNTIFS(Catálogo!$A$5:$A$201,"?*",Catálogo!$K$5:$K$201,"Sí")</f>
         <v>15</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B12" s="23" t="str">
         <f>IF(COUNTIFS(Catálogo!$A$5:$A$201,"?*",Catálogo!$E$5:$E$201,"Must")=COUNTIFS(Catálogo!$A$5:$A$201,"?*",Catálogo!$K$5:$K$201,"Sí"),"Coherente","REVISAR")</f>
         <v>Coherente</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B13" s="23">
         <f>COUNTIFS(Catálogo!$A$5:$A$201,"?*",Catálogo!$I$5:$I$201,"Validado")</f>
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B14" s="23">
         <f>COUNTIF(Catálogo!$L$5:$L$201,"Faltan campos")+COUNTIF(Catálogo!$L$5:$L$201,"Falta categoría")+COUNTIF(Catálogo!$L$5:$L$201,"Falta definir si integra el MVP")</f>
         <v>0</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B15" s="23">
         <f>COUNTIF(Trazabilidad!$A$5:$A$61,"?*")</f>
         <v>24</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B16" s="23">
         <f>COUNTIF(Trazabilidad!$F$5:$F$61,"Hallazgo sin destino")</f>
         <v>0</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B17" s="23">
         <f>COUNTIF(Entidades!$E$5:$E$45,"Entidad")</f>
         <v>9</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B18" s="23">
         <f>COUNTIF(Entidades!$A$5:$A$45,"?*")-COUNTIF(Entidades!$E$5:$E$45,"Entidad")</f>
         <v>4</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B19" s="23">
         <f>COUNTIF(Reglas!$C$5:$C$40,"?*")</f>
         <v>11</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B20" s="23">
         <f>COUNTIF(Reglas!$E$5:$E$40,"Pendiente")+COUNTIF(Reglas!$E$5:$E$40,"En disputa")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B21" s="23">
         <f>COUNTIF(Glosario!$E$5:$E$45,"Sí")</f>
         <v>4</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B22" s="23">
         <f>SUM(Iteraciones!$G$5:$G$12)</f>
         <v>176</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B23" s="23" t="str">
         <f>Recursos!$F$38</f>
         <v>Coherente</v>
       </c>
       <c r="C23" s="24" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B26" s="37"/>
       <c r="C26" s="37"/>

--- a/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
+++ b/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec7050e6095d21e4/Escritorio/Tesis/devolucion_AE2/build/_salida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EF7FC0DB537A4C5052A15F29E5FA04E3EBD19D46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_EE7F89B3657A9AD170B55FC9E497D0D422539C45" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -508,7 +508,7 @@
     <t>Usabilidad</t>
   </si>
   <si>
-    <t>Debe operar en la terminal de la ventanilla. La gerencia aprobó el requisito en el acta del 06/10/2026, pero la resolución real de ese monitor no se informó: queda pendiente fecharla.</t>
+    <t>Debe operar en la terminal de la ventanilla. La gerencia aprobó el requisito en el acta del 06/10/2026, pero la resolución real de ese monitor no se informó; la interfaz se diseña para 1366 × 768 px como mínimo.</t>
   </si>
   <si>
     <t>Condición inicial: navegador a 1366 × 768 px. Acción: recorrer apertura, consumo y cobro. Resultado: no aparece barra de desplazamiento horizontal y cada control tiene un área de clic de al menos 44 × 44 px, comprobada con las herramientas del navegador.</t>
@@ -574,7 +574,7 @@
     <t>Es la decisión de la AE1 para las intermitencias de internet (H-09); reemplaza la idea de persistencia local en caché, que no se sostiene con el servidor en la nube.</t>
   </si>
   <si>
-    <t>Condición inicial: tres turnos En Curso. Acción: cortar la conexión del navegador durante 10 min y restablecerla. Resultado: en 5 s o menos la grilla muestra los tres turnos con los minutos calculados por el servidor (diferencia de 1 min o menos respecto de su reloj), sin turnos perdidos ni duplicados. Durante el corte no se pueden abrir ni cobrar turnos; el procedimiento de contingencia manual no se definió en la sesión del 06/10/2026 y queda pendiente.</t>
+    <t>Condición inicial: tres turnos En Curso. Acción: cortar la conexión del navegador durante 10 min y restablecerla. Resultado: en 5 s o menos la grilla muestra los tres turnos con los minutos calculados por el servidor (diferencia de 1 min o menos respecto de su reloj), sin turnos perdidos ni duplicados. Durante el corte no se pueden abrir ni cobrar turnos; el procedimiento de contingencia manual no se definió en la sesión del 06/10/2026; el autor propone anotar los turnos en papel y cargarlos al volver la conexión.</t>
   </si>
   <si>
     <t>Matriz de trazabilidad · hallazgo de la AE1 → requisito</t>
@@ -1645,7 +1645,7 @@
     <t>equipo</t>
   </si>
   <si>
-    <t>Equipo del motel; sin costo para el proyecto. Resolución del monitor: pendiente de relevar (RNF-05).</t>
+    <t>Equipo del motel; sin costo para el proyecto. Resolución real del monitor no informada; se diseña para 1366 × 768 px (RNF-05).</t>
   </si>
   <si>
     <t>Terminal POSNET</t>
@@ -1708,7 +1708,7 @@
     <t>Soporte preventivo y correctivo posterior al despliegue</t>
   </si>
   <si>
-    <t>Estimación del autor: 2 h mensuales de guardia pactadas con la gerencia (pendiente de acuerdo).</t>
+    <t>Estimación del autor: 2 h mensuales de guardia posteriores al despliegue.</t>
   </si>
   <si>
     <t>Total general</t>
@@ -1987,7 +1987,7 @@
     <t>Monitor de 1366 × 768 en la ventanilla</t>
   </si>
   <si>
-    <t>Pendiente de relevar y fechar.</t>
+    <t>No informada por la gerencia; RNF-05 aprobado en el acta del 06/10/2026.</t>
   </si>
   <si>
     <t>Parálisis ante cortes de conectividad</t>
@@ -3773,7 +3773,7 @@
         <v>Fila completa</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>139</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>Fila completa</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="114" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="126" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>161</v>
       </c>
@@ -10761,7 +10761,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>518</v>
       </c>

--- a/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
+++ b/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec7050e6095d21e4/Escritorio/Tesis/devolucion_AE2/build/_salida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EE7F89B3657A9AD170B55FC9E497D0D422539C45" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_EE7F689BE173CCD170B55FC9E497D0D422539C45" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
+++ b/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec7050e6095d21e4/Escritorio/Tesis/devolucion_AE2/build/_salida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EE7F689BE173CCD170B55FC9E497D0D422539C45" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_0EB9F3FBB3D4F05D31A35FC9E4875BD76E728DAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,7 +256,7 @@
     <t>Automatiza la liquidación y elimina las sumas manuales de tiempos de estadía.</t>
   </si>
   <si>
-    <t>Condición inicial: tarifa Estándar vigente ($8.000 por 120 min y $2.500 por cada fracción de 30 min o porción, sin tolerancia) y un turno En Curso. Acción: pedir el resumen del turno a los 120, 121, 150 y 151 min. Resultado: sobreturno de $0, $2.500, $2.500 y $5.000; total = tarifa base + sobreturno + consumos (RN-DER-01 y RN-DER-02). La gerencia aprobó los importes de la tarifa en el acta del 06/10/2026; el acta del 23/09 había aprobado la regla.</t>
+    <t>Condición inicial: tarifa Estándar vigente ($8.000 por 120 min y $2.500 por cada fracción de 30 min o porción, sin tolerancia) y un turno En Curso. Acción: pedir el resumen del turno a los 120, 121, 150 y 151 min. Resultado: sobreturno de $0, $2.500, $2.500 y $5.000; total = tarifa base + sobreturno + consumos (RN-DER-01 y RN-DER-02). La gerencia aprueba los importes de la tarifa en el acta del 06/10/2026; el acta del 23/09 aprueba la regla.</t>
   </si>
   <si>
     <t>H-05, H-07, H-16 · Acta 23/09</t>
@@ -457,7 +457,7 @@
     <t>El cobro debe resolverse en un paso, sin demorar al cliente en la salida (H-08).</t>
   </si>
   <si>
-    <t>Condición inicial: API en el entorno de despliegue con 5 peticiones concurrentes de apertura y 5 de cobro. Acción: repetir 20 veces y medir la latencia. Resultado: el percentil 95 es de 800 ms o menos. La gerencia aprobó el umbral en el acta del 06/10/2026.</t>
+    <t>Condición inicial: API en el entorno de despliegue con 5 peticiones concurrentes de apertura y 5 de cobro. Acción: repetir 20 veces y medir la latencia. Resultado: el percentil 95 es de 800 ms o menos. La gerencia aprueba el umbral en el acta del 06/10/2026.</t>
   </si>
   <si>
     <t>H-02, H-08, H-14 · Acta 23/09</t>
@@ -493,7 +493,7 @@
     <t>El cierre ciego necesita saber a quién atribuir un faltante (RF-09) y la AE1 exige delimitar responsabilidades (H-06).</t>
   </si>
   <si>
-    <t>Condición inicial: dos conserjes con credenciales propias. Acción: un conserje inicia sesión y ejecuta una apertura y un cobro; desde la consola del navegador se ejecuta document.cookie. Resultado: el token JWT no es visible (cookie httpOnly), el turno y el pago registran el identificador de ese operador y una petición sin token responde 401. La gerencia aprobó el requisito en el acta del 06/10/2026; el mecanismo se decide en el prototipo v2.</t>
+    <t>Condición inicial: dos conserjes con credenciales propias. Acción: un conserje inicia sesión y ejecuta una apertura y un cobro; desde la consola del navegador se ejecuta document.cookie. Resultado: el token JWT no es visible (cookie httpOnly), el turno y el pago registran el identificador de ese operador y una petición sin token responde 401. La gerencia aprueba el requisito en el acta del 06/10/2026; el mecanismo se decide en el prototipo v2.</t>
   </si>
   <si>
     <t>H-06, H-17 · Acta 23/09</t>
@@ -508,7 +508,7 @@
     <t>Usabilidad</t>
   </si>
   <si>
-    <t>Debe operar en la terminal de la ventanilla. La gerencia aprobó el requisito en el acta del 06/10/2026, pero la resolución real de ese monitor no se informó; la interfaz se diseña para 1366 × 768 px como mínimo.</t>
+    <t>Debe operar en la terminal de la ventanilla. La gerencia aprueba el requisito en el acta del 06/10/2026, pero la resolución real de ese monitor no se informa; la interfaz se diseña para 1366 × 768 px como mínimo.</t>
   </si>
   <si>
     <t>Condición inicial: navegador a 1366 × 768 px. Acción: recorrer apertura, consumo y cobro. Resultado: no aparece barra de desplazamiento horizontal y cada control tiene un área de clic de al menos 44 × 44 px, comprobada con las herramientas del navegador.</t>
@@ -556,7 +556,7 @@
     <t>La patente de un turno se elimina dentro de las 24 h posteriores a su cierre.</t>
   </si>
   <si>
-    <t>La patente identifica de forma indirecta al titular del vehículo; se conserva mientras el vehículo está en el motel y luego se elimina (Ley 25.326, art. 4, inc. 7). La gerencia aprobó las 24 h en el acta del 06/10/2026 y declaró que necesita la patente por razones de seguridad; informó que no hay indicación del asesor legal.</t>
+    <t>La patente identifica de forma indirecta al titular del vehículo; se conserva mientras el vehículo está en el motel y luego se elimina (Ley 25.326, art. 4, inc. 7). La gerencia aprueba las 24 h en el acta del 06/10/2026, declara que necesita la patente por razones de seguridad e informa que no hay indicación del asesor legal.</t>
   </si>
   <si>
     <t>Condición inicial: turno FINALIZADO con patente AE987CD, cerrado hace más de 24 h. Acción: ejecutar la depuración y consultar los turnos cerrados y la tabla de estadía activa. Resultado: ninguna patente de un turno cerrado hace más de 24 h permanece almacenada (la consulta devuelve 0 filas) y los importes del turno quedan intactos, sin deshabilitar los triggers de inmutabilidad.</t>
@@ -574,7 +574,7 @@
     <t>Es la decisión de la AE1 para las intermitencias de internet (H-09); reemplaza la idea de persistencia local en caché, que no se sostiene con el servidor en la nube.</t>
   </si>
   <si>
-    <t>Condición inicial: tres turnos En Curso. Acción: cortar la conexión del navegador durante 10 min y restablecerla. Resultado: en 5 s o menos la grilla muestra los tres turnos con los minutos calculados por el servidor (diferencia de 1 min o menos respecto de su reloj), sin turnos perdidos ni duplicados. Durante el corte no se pueden abrir ni cobrar turnos; el procedimiento de contingencia manual no se definió en la sesión del 06/10/2026; el autor propone anotar los turnos en papel y cargarlos al volver la conexión.</t>
+    <t>Condición inicial: tres turnos En Curso. Acción: cortar la conexión del navegador durante 10 min y restablecerla. Resultado: en 5 s o menos la grilla muestra los tres turnos con los minutos calculados por el servidor (diferencia de 1 min o menos respecto de su reloj), sin turnos perdidos ni duplicados. Durante el corte no se pueden abrir ni cobrar turnos; el procedimiento de contingencia manual no se define en la sesión del 06/10/2026; el autor propone anotar los turnos en papel y cargarlos al volver la conexión.</t>
   </si>
   <si>
     <t>Matriz de trazabilidad · hallazgo de la AE1 → requisito</t>
@@ -604,7 +604,7 @@
     <t>H-01</t>
   </si>
   <si>
-    <t>13 habitaciones, 3 guardias diarias y unos 30 turnos por día hábil (lunes a jueves) y unos 40 en fin de semana (viernes a domingo). La AE1 original informaba 20 a 30 y 40 a 50; rige lo que la gerencia dijo en la entrevista.</t>
+    <t>13 habitaciones, 3 guardias diarias y unos 30 turnos por día hábil (lunes a jueves) y unos 40 en fin de semana (viernes a domingo). La AE1 original informa 20 a 30 y 40 a 50; rige lo que la gerencia dice en la entrevista.</t>
   </si>
   <si>
     <t>AE1 · II.3 (v2) y entrevista, pág. 1</t>
@@ -718,7 +718,7 @@
     <t>H-11</t>
   </si>
   <si>
-    <t>El personal de maestranza y limpieza quedó fuera del relevamiento; los tiempos de limpieza son estimaciones indirectas de conserjería.</t>
+    <t>El personal de maestranza y limpieza queda fuera del relevamiento; los tiempos de limpieza son estimaciones indirectas de conserjería.</t>
   </si>
   <si>
     <t>AE1 · II.2 y II.6 (limitaciones)</t>
@@ -1384,7 +1384,7 @@
     <t>RF-08, RF-09, RNF-02, RNF-04, RNF-08 (5 Must) y RNF-07</t>
   </si>
   <si>
-    <t>Prototipo v2: cierre ciego con pruebas automáticas. La retención de la patente (RNF-08) y el rol de aplicación se adelantaron a la v1.2 (05/10/2026).</t>
+    <t>Prototipo v2: cierre ciego con pruebas automáticas. La retención de la patente (RNF-08) y el rol de aplicación se adelantan a la v1.2 (05/10/2026).</t>
   </si>
   <si>
     <t>02/11/2026</t>
@@ -9598,7 +9598,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>3</v>
       </c>

--- a/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
+++ b/docs/AE2/20261005_CatalogoRequisitos_ThiagoLeal_v3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec7050e6095d21e4/Escritorio/Tesis/devolucion_AE2/build/_salida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_0EB9F3FBB3D4F05D31A35FC9E4875BD76E728DAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_0EB9574B43C51080F1AF5F29E4BA83D0C872A235" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -508,13 +508,13 @@
     <t>Usabilidad</t>
   </si>
   <si>
-    <t>Debe operar en la terminal de la ventanilla. La gerencia aprueba el requisito en el acta del 06/10/2026, pero la resolución real de ese monitor no se informa; la interfaz se diseña para 1366 × 768 px como mínimo.</t>
+    <t>Debe operar en la terminal de la ventanilla. La gerencia aprueba el requisito en el acta del 06/10/2026 y el autor relevó en el local que ese monitor es de 1366 × 768 px.</t>
   </si>
   <si>
     <t>Condición inicial: navegador a 1366 × 768 px. Acción: recorrer apertura, consumo y cobro. Resultado: no aparece barra de desplazamiento horizontal y cada control tiene un área de clic de al menos 44 × 44 px, comprobada con las herramientas del navegador.</t>
   </si>
   <si>
-    <t>Sin hallazgo: relevar y fechar la resolución del monitor de la ventanilla · Acta 23/09</t>
+    <t>Sin hallazgo: relevamiento del autor en el local (monitor de 1366 × 768 px) · Acta 23/09</t>
   </si>
   <si>
     <t>RNF-06</t>
@@ -1645,7 +1645,7 @@
     <t>equipo</t>
   </si>
   <si>
-    <t>Equipo del motel; sin costo para el proyecto. Resolución real del monitor no informada; se diseña para 1366 × 768 px (RNF-05).</t>
+    <t>Equipo del motel; sin costo para el proyecto. Monitor de 1366 × 768 px, relevado por el autor (RNF-05).</t>
   </si>
   <si>
     <t>Terminal POSNET</t>
@@ -1987,7 +1987,7 @@
     <t>Monitor de 1366 × 768 en la ventanilla</t>
   </si>
   <si>
-    <t>No informada por la gerencia; RNF-05 aprobado en el acta del 06/10/2026.</t>
+    <t>Relevada por el autor en el local: 1366 × 768 px; RNF-05 aprobado en el acta del 06/10/2026.</t>
   </si>
   <si>
     <t>Parálisis ante cortes de conectividad</t>
@@ -3773,7 +3773,7 @@
         <v>Fila completa</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>139</v>
       </c>
@@ -10761,7 +10761,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>518</v>
       </c>
